--- a/schools-presentations/A Gymnasiou/kahoot/A5.2 Μ3 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου.xlsx
+++ b/schools-presentations/A Gymnasiou/kahoot/A5.2 Μ3 - Διαχείριση Ηλεκτρονικού Ταχυδρομείου.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kahoot Quiz" sheetId="1" r:id="R64e0e90cb67a43c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Kahoot Quiz" sheetId="1" r:id="R868f0bddcc064789"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -55,7 +55,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF4CC"/>
+        <x:fgColor rgb="FFFFF1C7"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -340,30 +340,30 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="38" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="31" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="31" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="31" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="31" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="42" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="34" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="34" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="34" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="34" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="16" hidden="0" customWidth="1"/>
     <x:col min="7" max="7" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="42" customHeight="1">
       <x:c r="A1" s="6" t="str">
-        <x:v>Question - max 95 characters</x:v>
+        <x:v>Question - max 120 characters</x:v>
       </x:c>
       <x:c r="B1" s="6" t="str">
-        <x:v>Answer 1 - max 60 characters</x:v>
+        <x:v>Answer 1 - max 75 characters</x:v>
       </x:c>
       <x:c r="C1" s="6" t="str">
-        <x:v>Answer 2 - max 60 characters</x:v>
+        <x:v>Answer 2 - max 75 characters</x:v>
       </x:c>
       <x:c r="D1" s="6" t="str">
-        <x:v>Answer 3 - max 60 characters</x:v>
+        <x:v>Answer 3 - max 75 characters</x:v>
       </x:c>
       <x:c r="E1" s="6" t="str">
-        <x:v>Answer 4 - max 60 characters</x:v>
+        <x:v>Answer 4 - max 75 characters</x:v>
       </x:c>
       <x:c r="F1" s="6" t="str">
         <x:v>Time limit (sec)</x:v>
@@ -372,21 +372,21 @@
         <x:v>Correct answer(s)</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="58" customHeight="1">
+    <x:row r="2" ht="62" customHeight="1">
       <x:c r="A2" s="11" t="str">
         <x:v>Τι είναι ένα επισυναπτόμενο αρχείο (Attachment);</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>Αρχείο που αποστέλλεται μαζί με μήνυμα e-mail</x:v>
+        <x:v>Αρχείο που αποστέλλεται μαζί με το e-mail</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>Μήνυμα χωρίς παραλήπτη</x:v>
+        <x:v>Αντίγραφο του μηνύματος στα Πρόχειρα</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>Επαφή από το βιβλίο διευθύνσεων</x:v>
+        <x:v>Σύνδεσμος προς το Βιβλίο Διευθύνσεων</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>Φάκελος με διαγραμμένα μηνύματα</x:v>
+        <x:v>Μήνυμα που δεν έχει παραλήπτη</x:v>
       </x:c>
       <x:c r="F2" s="14" t="n">
         <x:v>30</x:v>
@@ -395,211 +395,211 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="58" customHeight="1">
+    <x:row r="3" ht="62" customHeight="1">
       <x:c r="A3" s="11" t="str">
         <x:v>Ποια εντολή χρησιμοποιούμε για να προσθέσουμε αρχείο σε μήνυμα;</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
+        <x:v>Reply all</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="str">
+        <x:v>Forward</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="str">
+        <x:v>Save</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="str">
         <x:v>Attach ή Επισύναψη</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="str">
-        <x:v>Reply all</x:v>
-      </x:c>
-      <x:c r="D3" s="11" t="str">
-        <x:v>Delete</x:v>
-      </x:c>
-      <x:c r="E3" s="11" t="str">
-        <x:v>Refresh</x:v>
       </x:c>
       <x:c r="F3" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G3" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="58" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="62" customHeight="1">
       <x:c r="A4" s="11" t="str">
-        <x:v>Μπορούμε να επισυνάψουμε περισσότερα από ένα αρχεία;</x:v>
+        <x:v>Μπορούμε να επισυνάψουμε περισσότερα από ένα αρχεία στο ίδιο μήνυμα;</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>Ναι, μπορούμε να επισυνάψουμε πολλά αρχεία</x:v>
+        <x:v>Μόνο αν είναι όλα εικόνες</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>Όχι, επιτρέπεται μόνο ένα αρχείο</x:v>
+        <x:v>Ναι, εφόσον δεν ξεπερνούν τα επιτρεπόμενα όρια</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>Μόνο αν είναι όλα εικόνες</x:v>
+        <x:v>Μόνο αν έχουν ακριβώς το ίδιο όνομα</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>Μόνο αν έχουν το ίδιο όνομα</x:v>
+        <x:v>Μόνο όταν στέλνουμε το μήνυμα στον εαυτό μας</x:v>
       </x:c>
       <x:c r="F4" s="14" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G4" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="58" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="62" customHeight="1">
       <x:c r="A5" s="11" t="str">
-        <x:v>Μπορούν τα επισυναπτόμενα αρχεία να είναι διαφορετικού τύπου;</x:v>
+        <x:v>Μπορούν τα συνημμένα αρχεία να είναι διαφορετικού τύπου;</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Ναι, μπορούν να είναι διαφορετικού τύπου</x:v>
+        <x:v>Όχι, πρέπει να έχουν την ίδια κατάληξη</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>Όχι, πρέπει να είναι όλα αρχεία κειμένου</x:v>
+        <x:v>Μόνο αν είναι όλα μικρότερα από 1 KB</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>Μόνο εικόνες και τίποτε άλλο</x:v>
+        <x:v>Ναι, π.χ. ένα PDF και μία εικόνα</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>Μόνο αρχεία του ίδιου μεγέθους</x:v>
+        <x:v>Μόνο αν δημιουργήθηκαν με το ίδιο πρόγραμμα</x:v>
       </x:c>
       <x:c r="F5" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G5" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="58" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="62" customHeight="1">
       <x:c r="A6" s="11" t="str">
-        <x:v>Τι μπορούμε να κάνουμε με ένα επισυναπτόμενο που λάβαμε;</x:v>
+        <x:v>Τι μπορούμε να κάνουμε με ένα συνημμένο που λάβαμε από έμπιστο αποστολέα;</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
         <x:v>Να το ανοίξουμε ή να το αποθηκεύσουμε</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>Μόνο να το διαγράψουμε</x:v>
+        <x:v>Να το δούμε μόνο μέσα στο πεδίο Subject</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>Μόνο να το προωθήσουμε</x:v>
+        <x:v>Να το μεταφέρουμε μόνο στα Sent</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>Να το δούμε μόνο μέσα στο θέμα</x:v>
+        <x:v>Να το ανοίξουμε χωρίς κανέναν έλεγχο</x:v>
       </x:c>
       <x:c r="F6" s="14" t="n">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="G6" s="14" t="str">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="58" customHeight="1">
+    <x:row r="7" ht="62" customHeight="1">
       <x:c r="A7" s="11" t="str">
-        <x:v>Πού αποθηκεύεται ένα επισυναπτόμενο όταν επιλέξουμε Αποθήκευση;</x:v>
+        <x:v>Πού αποθηκεύεται ένα συνημμένο όταν επιλέξουμε Download ή Save;</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Στον φάκελο που επιλέγουμε στον υπολογιστή</x:v>
+        <x:v>Πάντα μέσα στο ίδιο το μήνυμα</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>Μόνο στα Εισερχόμενα</x:v>
+        <x:v>Αυτόματα στο Βιβλίο Διευθύνσεων</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>Αυτόματα στο Βιβλίο Διευθύνσεων</x:v>
+        <x:v>Μόνο στον φάκελο Sent</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>Μόνο στα Απεσταλμένα</x:v>
+        <x:v>Στον φάκελο λήψεων ή σε φάκελο που επιλέγουμε</x:v>
       </x:c>
       <x:c r="F7" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G7" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="58" customHeight="1">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="62" customHeight="1">
       <x:c r="A8" s="11" t="str">
-        <x:v>Ποιο σύμβολο χρησιμοποιείται συχνά για την Επισύναψη;</x:v>
+        <x:v>Ποιο σύμβολο χρησιμοποιείται συνήθως για το Attachment;</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
+        <x:v>Ένας κάδος ανακύκλωσης</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
         <x:v>Ένας συνδετήρας</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="str">
-        <x:v>Ένα σπίτι</x:v>
-      </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>Ένας κάδος</x:v>
+        <x:v>Ένα βέλος απάντησης</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>Ένα βέλος επιστροφής</x:v>
+        <x:v>Ένα εικονίδιο αρχικής σελίδας</x:v>
       </x:c>
       <x:c r="F8" s="14" t="n">
         <x:v>20</x:v>
       </x:c>
       <x:c r="G8" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="58" customHeight="1">
+        <x:v>2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="62" customHeight="1">
       <x:c r="A9" s="11" t="str">
-        <x:v>Πότε επιλέγουμε τα αρχεία που θέλουμε να επισυνάψουμε;</x:v>
+        <x:v>Πότε πρέπει να ελέγξουμε ότι προστέθηκε το σωστό συνημμένο;</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>Κατά τη σύνταξη του μηνύματος πριν την αποστολή</x:v>
+        <x:v>Μόνο αφού λάβει απάντηση ο παραλήπτης</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>Μετά την οριστική αποστολή του μηνύματος</x:v>
+        <x:v>Αφού διαγράψουμε το αρχικό αρχείο</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>Μόνο αφού διαγράψουμε το μήνυμα</x:v>
+        <x:v>Πριν πατήσουμε Send</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>Αφού αποσυνδεθούμε από τον λογαριασμό</x:v>
+        <x:v>Μετά την αποσύνδεση από τον λογαριασμό</x:v>
       </x:c>
       <x:c r="F9" s="14" t="n">
         <x:v>30</x:v>
       </x:c>
       <x:c r="G9" s="14" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="58" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="62" customHeight="1">
       <x:c r="A10" s="13" t="str">
-        <x:v>Θέλεις να στείλεις δύο φωτογραφίες. Ποια είναι η σωστή σειρά;</x:v>
+        <x:v>Στέλνεις εργασία και φωτογραφία. Ποια σειρά ενεργειών είναι ασφαλέστερη;</x:v>
       </x:c>
       <x:c r="B10" s="12" t="str">
-        <x:v>Νέο μήνυμα → Attach → επιλογή αρχείων → Αποστολή</x:v>
+        <x:v>Attach → Send → επιλογή αρχείων → έλεγχος</x:v>
       </x:c>
       <x:c r="C10" s="12" t="str">
-        <x:v>Attach → Αποσύνδεση → Νέο μήνυμα → Διαγραφή</x:v>
+        <x:v>Νέο μήνυμα → επιλογή αρχείων → Send → παραλήπτης</x:v>
       </x:c>
       <x:c r="D10" s="12" t="str">
-        <x:v>Αποστολή → Attach → επιλογή αρχείων</x:v>
+        <x:v>Νέο μήνυμα → Attach → επιλογή αρχείων → έλεγχος → Send</x:v>
       </x:c>
       <x:c r="E10" s="12" t="str">
-        <x:v>Νέο μήνυμα → Διαγραφή → Attach → Αποστολή</x:v>
+        <x:v>Send → αποθήκευση στα Drafts → Attach</x:v>
       </x:c>
       <x:c r="F10" s="15" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="G10" s="15" t="str">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="58" customHeight="1">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="62" customHeight="1">
       <x:c r="A11" s="13" t="str">
-        <x:v>Λαμβάνεις δύο συνημμένα και τα θέλεις σε συγκεκριμένο φάκελο. Τι κάνεις;</x:v>
+        <x:v>Λαμβάνεις απρόσμενο ZIP από άγνωστο αποστολέα. Τι κάνεις;</x:v>
       </x:c>
       <x:c r="B11" s="12" t="str">
-        <x:v>Τα ανοίγεις μόνο μέσα από το μήνυμα</x:v>
+        <x:v>Δεν το ανοίγω· ελέγχω τον αποστολέα και το αναφέρω αν χρειάζεται</x:v>
       </x:c>
       <x:c r="C11" s="12" t="str">
-        <x:v>Τα προωθείς στον εαυτό σου</x:v>
+        <x:v>Το ανοίγω επειδή ένα ZIP περιέχει πάντα ασφαλή αρχεία</x:v>
       </x:c>
       <x:c r="D11" s="12" t="str">
-        <x:v>Επιλέγεις αποθήκευση και τον σωστό φάκελο</x:v>
+        <x:v>Το προωθώ σε συμμαθητή για να ελέγξει το περιεχόμενο</x:v>
       </x:c>
       <x:c r="E11" s="12" t="str">
-        <x:v>Μετακινείς το μήνυμα στα Απεσταλμένα</x:v>
+        <x:v>Το μετονομάζω σε PDF και μετά το ανοίγω</x:v>
       </x:c>
       <x:c r="F11" s="15" t="n">
         <x:v>60</x:v>
       </x:c>
       <x:c r="G11" s="15" t="str">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
